--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484049_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484049_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.1674</v>
+        <v>6.0778</v>
       </c>
       <c r="E2" t="n">
-        <v>4.4833</v>
+        <v>4.506</v>
       </c>
       <c r="F2" t="n">
-        <v>1.6841</v>
+        <v>1.5719</v>
       </c>
       <c r="G2" t="n">
         <v>2.3423</v>
@@ -610,13 +610,13 @@
         <v>2.579</v>
       </c>
       <c r="S2" t="n">
-        <v>1.0191</v>
+        <v>0.9295</v>
       </c>
       <c r="T2" t="n">
-        <v>1.1054</v>
+        <v>1.1281</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.0863</v>
+        <v>-0.1985</v>
       </c>
       <c r="V2" t="n">
         <v>2.6076</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>D. FONT RODRIGUEZ</t>
+          <t>G. SEVILLANO PUIG</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.7922</v>
+        <v>5.2405</v>
       </c>
       <c r="E3" t="n">
-        <v>3.8429</v>
+        <v>3.9288</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9494</v>
+        <v>1.3117</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8689</v>
+        <v>1.0594</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.3205</v>
+        <v>1.4158</v>
       </c>
       <c r="I3" t="n">
-        <v>2.1894</v>
+        <v>-0.3564</v>
       </c>
       <c r="J3" t="n">
-        <v>0.7019</v>
+        <v>2.0729</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.3926</v>
+        <v>1.6585</v>
       </c>
       <c r="L3" t="n">
-        <v>1.0946</v>
+        <v>0.4144</v>
       </c>
       <c r="M3" t="n">
-        <v>0.167</v>
+        <v>-1.0135</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.9278</v>
+        <v>-0.2428</v>
       </c>
       <c r="O3" t="n">
-        <v>1.0948</v>
+        <v>-0.7707000000000001</v>
       </c>
       <c r="P3" t="n">
-        <v>1.3887</v>
+        <v>-0.3968</v>
       </c>
       <c r="Q3" t="n">
+        <v>-3.1741</v>
+      </c>
+      <c r="R3" t="n">
+        <v>2.7774</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0.4265</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0.8787</v>
+      </c>
+      <c r="U3" t="n">
+        <v>-0.4521</v>
+      </c>
+      <c r="V3" t="n">
+        <v>4.1513</v>
+      </c>
+      <c r="W3" t="n">
+        <v>4.1513</v>
+      </c>
+      <c r="X3" t="n">
         <v>0</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.3887</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0.725</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0.7993</v>
-      </c>
-      <c r="U3" t="n">
-        <v>-0.0743</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.8097</v>
-      </c>
-      <c r="W3" t="n">
-        <v>2.3417</v>
-      </c>
-      <c r="X3" t="n">
-        <v>-0.532</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>G. SEVILLANO PUIG</t>
+          <t>D. FONT RODRIGUEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.6593</v>
+        <v>4.5306</v>
       </c>
       <c r="E4" t="n">
-        <v>3.6</v>
+        <v>3.4971</v>
       </c>
       <c r="F4" t="n">
-        <v>1.0592</v>
+        <v>1.0335</v>
       </c>
       <c r="G4" t="n">
-        <v>1.0594</v>
+        <v>0.8689</v>
       </c>
       <c r="H4" t="n">
-        <v>1.4158</v>
+        <v>-1.3205</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3564</v>
+        <v>2.1894</v>
       </c>
       <c r="J4" t="n">
-        <v>2.0729</v>
+        <v>0.7019</v>
       </c>
       <c r="K4" t="n">
-        <v>1.6585</v>
+        <v>-0.3926</v>
       </c>
       <c r="L4" t="n">
-        <v>0.4144</v>
+        <v>1.0946</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.0135</v>
+        <v>0.167</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.2428</v>
+        <v>-0.9278</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.7707000000000001</v>
+        <v>1.0948</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.3968</v>
+        <v>1.3887</v>
       </c>
       <c r="Q4" t="n">
-        <v>-3.1741</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.7774</v>
+        <v>1.3887</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.1547</v>
+        <v>0.4634</v>
       </c>
       <c r="T4" t="n">
-        <v>0.5499000000000001</v>
+        <v>0.4535</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.7046</v>
+        <v>0.0098</v>
       </c>
       <c r="V4" t="n">
-        <v>4.1513</v>
+        <v>1.8097</v>
       </c>
       <c r="W4" t="n">
-        <v>4.1513</v>
+        <v>2.3417</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-0.532</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.2004</v>
+        <v>3.2714</v>
       </c>
       <c r="E5" t="n">
-        <v>1.8974</v>
+        <v>2.9403</v>
       </c>
       <c r="F5" t="n">
-        <v>0.303</v>
+        <v>0.3311</v>
       </c>
       <c r="G5" t="n">
         <v>0.9931</v>
@@ -844,13 +844,13 @@
         <v>1.7855</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.8089</v>
+        <v>0.2621</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.4988</v>
+        <v>0.5442</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3101</v>
+        <v>-0.2821</v>
       </c>
       <c r="V5" t="n">
         <v>2.4129</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.0067</v>
+        <v>0.0213</v>
       </c>
       <c r="E6" t="n">
         <v>-0.1582</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1515</v>
+        <v>0.1796</v>
       </c>
       <c r="G6" t="n">
         <v>0.1106</v>
@@ -922,13 +922,13 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0.081</v>
+        <v>0.1091</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>0.081</v>
+        <v>0.1091</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X. GUIA HORMIGON</t>
+          <t>M. ESTEBAN CALVO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,58 +955,58 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.8983</v>
+        <v>-0.5386</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.8094</v>
+        <v>0.5465</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.08890000000000001</v>
+        <v>-1.0851</v>
       </c>
       <c r="G7" t="n">
-        <v>1.6498</v>
+        <v>-0.6372</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.2171</v>
+        <v>-0.9429</v>
       </c>
       <c r="I7" t="n">
-        <v>1.8669</v>
+        <v>0.3057</v>
       </c>
       <c r="J7" t="n">
-        <v>1.4861</v>
+        <v>0.0533</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0403</v>
+        <v>0.0456</v>
       </c>
       <c r="L7" t="n">
-        <v>1.4458</v>
+        <v>0.0077</v>
       </c>
       <c r="M7" t="n">
-        <v>0.1637</v>
+        <v>-0.6905</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.2574</v>
+        <v>-0.9885</v>
       </c>
       <c r="O7" t="n">
-        <v>0.4211</v>
+        <v>0.2981</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.1903</v>
+        <v>1.3887</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.9838</v>
+        <v>-0.1984</v>
       </c>
       <c r="R7" t="n">
-        <v>0.7935</v>
+        <v>1.5871</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1514</v>
+        <v>-0.08359999999999999</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3117</v>
+        <v>0.6916</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1603</v>
+        <v>-0.7752</v>
       </c>
       <c r="V7" t="n">
         <v>-1.2065</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. ALEXANDRE</t>
+          <t>X. GUIA HORMIGON</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.2979</v>
+        <v>-0.5642</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.3884</v>
+        <v>-0.5033</v>
       </c>
       <c r="F8" t="n">
-        <v>1.0905</v>
+        <v>-0.0608</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.1769</v>
+        <v>1.6498</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.8595</v>
+        <v>-0.2171</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.3173</v>
+        <v>1.8669</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.1341</v>
+        <v>1.4861</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.3349</v>
+        <v>0.0403</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2008</v>
+        <v>1.4458</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.0428</v>
+        <v>0.1637</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.5246</v>
+        <v>-0.2574</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.5182</v>
+        <v>0.4211</v>
       </c>
       <c r="P8" t="n">
+        <v>-1.1903</v>
+      </c>
+      <c r="Q8" t="n">
         <v>-1.9838</v>
       </c>
-      <c r="Q8" t="n">
-        <v>-3.1741</v>
-      </c>
       <c r="R8" t="n">
-        <v>1.1903</v>
+        <v>0.7935</v>
       </c>
       <c r="S8" t="n">
-        <v>0.7158</v>
+        <v>0.1828</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1814</v>
+        <v>-0.0056</v>
       </c>
       <c r="U8" t="n">
-        <v>0.5344</v>
+        <v>0.1884</v>
       </c>
       <c r="V8" t="n">
-        <v>2.1469</v>
+        <v>-1.2065</v>
       </c>
       <c r="W8" t="n">
-        <v>1.7384</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0.4085</v>
+        <v>-1.2065</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. ESTEBAN CALVO</t>
+          <t>A. ALEXANDRE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.3636</v>
+        <v>-1.4881</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.026</v>
+        <v>-2.3261</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.3376</v>
+        <v>0.838</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.6372</v>
+        <v>-2.1769</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.9429</v>
+        <v>-1.8595</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3057</v>
+        <v>-0.3173</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0533</v>
+        <v>-1.1341</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0456</v>
+        <v>-1.3349</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0077</v>
+        <v>0.2008</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.6905</v>
+        <v>-1.0428</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.9885</v>
+        <v>-0.5246</v>
       </c>
       <c r="O9" t="n">
-        <v>0.2981</v>
+        <v>-0.5182</v>
       </c>
       <c r="P9" t="n">
-        <v>1.3887</v>
+        <v>-1.9838</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.1984</v>
+        <v>-3.1741</v>
       </c>
       <c r="R9" t="n">
-        <v>1.5871</v>
+        <v>1.1903</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.9086</v>
+        <v>0.5256999999999999</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1191</v>
+        <v>0.2438</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.0277</v>
+        <v>0.2819</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.2065</v>
+        <v>2.1469</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.7384</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.2065</v>
+        <v>0.4085</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>D. KRAMER</t>
+          <t>X. ISERN MAZA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,64 +1189,64 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.0469</v>
+        <v>-2.5123</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.6323</v>
+        <v>-0.981</v>
       </c>
       <c r="F10" t="n">
-        <v>0.5854</v>
+        <v>-1.5313</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.1682</v>
+        <v>1.0394</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.7564</v>
+        <v>0.5289</v>
       </c>
       <c r="I10" t="n">
-        <v>0.5883</v>
+        <v>0.5105</v>
       </c>
       <c r="J10" t="n">
-        <v>-2.2121</v>
+        <v>1.751</v>
       </c>
       <c r="K10" t="n">
-        <v>-2.3727</v>
+        <v>0.9879</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1606</v>
+        <v>0.7631</v>
       </c>
       <c r="M10" t="n">
-        <v>0.0439</v>
+        <v>-0.7116</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.3837</v>
+        <v>-0.459</v>
       </c>
       <c r="O10" t="n">
-        <v>0.4276</v>
+        <v>-0.2526</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.3887</v>
+        <v>-2.3806</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.1741</v>
+        <v>-3.3725</v>
       </c>
       <c r="R10" t="n">
-        <v>1.7855</v>
+        <v>0.9919</v>
       </c>
       <c r="S10" t="n">
-        <v>2.1845</v>
+        <v>0.0354</v>
       </c>
       <c r="T10" t="n">
-        <v>2.222</v>
+        <v>0.6405</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0376</v>
+        <v>-0.6051</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.6745</v>
+        <v>-1.2065</v>
       </c>
       <c r="W10" t="n">
-        <v>0.532</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
         <v>-1.2065</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X. ISERN MAZA</t>
+          <t>D. KRAMER</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,64 +1267,64 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.1322</v>
+        <v>-3.3415</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.5729</v>
+        <v>-3.5902</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.5593</v>
+        <v>0.2487</v>
       </c>
       <c r="G11" t="n">
-        <v>1.0394</v>
+        <v>-2.1682</v>
       </c>
       <c r="H11" t="n">
-        <v>0.5289</v>
+        <v>-2.7564</v>
       </c>
       <c r="I11" t="n">
-        <v>0.5105</v>
+        <v>0.5883</v>
       </c>
       <c r="J11" t="n">
-        <v>1.751</v>
+        <v>-2.2121</v>
       </c>
       <c r="K11" t="n">
-        <v>0.9879</v>
+        <v>-2.3727</v>
       </c>
       <c r="L11" t="n">
-        <v>0.7631</v>
+        <v>0.1606</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.7116</v>
+        <v>0.0439</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.459</v>
+        <v>-0.3837</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.2526</v>
+        <v>0.4276</v>
       </c>
       <c r="P11" t="n">
-        <v>-2.3806</v>
+        <v>-1.3887</v>
       </c>
       <c r="Q11" t="n">
-        <v>-3.3725</v>
+        <v>-3.1741</v>
       </c>
       <c r="R11" t="n">
-        <v>0.9919</v>
+        <v>1.7855</v>
       </c>
       <c r="S11" t="n">
-        <v>0.4155</v>
+        <v>0.8899</v>
       </c>
       <c r="T11" t="n">
-        <v>1.0487</v>
+        <v>1.2641</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.6332</v>
+        <v>-0.3742</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.2065</v>
+        <v>-0.6745</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>0.532</v>
       </c>
       <c r="X11" t="n">
         <v>-1.2065</v>
@@ -1345,16 +1345,16 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>10.0737</v>
+        <v>10.6969</v>
       </c>
       <c r="E12" t="n">
-        <v>7.2364</v>
+        <v>7.859900000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>2.837299999999999</v>
+        <v>2.8373</v>
       </c>
       <c r="G12" t="n">
-        <v>3.0812</v>
+        <v>3.081199999999999</v>
       </c>
       <c r="H12" t="n">
         <v>-5.0159</v>
@@ -1390,13 +1390,13 @@
         <v>14.8789</v>
       </c>
       <c r="S12" t="n">
-        <v>3.1173</v>
+        <v>3.7408</v>
       </c>
       <c r="T12" t="n">
-        <v>5.2153</v>
+        <v>5.838900000000001</v>
       </c>
       <c r="U12" t="n">
-        <v>-2.0981</v>
+        <v>-2.098</v>
       </c>
       <c r="V12" t="n">
         <v>8.8344</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.3982</v>
+        <v>4.2324</v>
       </c>
       <c r="E13" t="n">
-        <v>2.2719</v>
+        <v>1.9658</v>
       </c>
       <c r="F13" t="n">
-        <v>2.1263</v>
+        <v>2.2666</v>
       </c>
       <c r="G13" t="n">
         <v>2.3432</v>
@@ -1468,13 +1468,13 @@
         <v>3.3725</v>
       </c>
       <c r="S13" t="n">
-        <v>0.1389</v>
+        <v>-0.0269</v>
       </c>
       <c r="T13" t="n">
-        <v>1.3038</v>
+        <v>0.9977</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.1649</v>
+        <v>-1.0246</v>
       </c>
       <c r="V13" t="n">
         <v>-0.4645</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.9771</v>
+        <v>3.7424</v>
       </c>
       <c r="E14" t="n">
-        <v>1.871</v>
+        <v>1.973</v>
       </c>
       <c r="F14" t="n">
-        <v>2.1061</v>
+        <v>1.7694</v>
       </c>
       <c r="G14" t="n">
         <v>4.6153</v>
@@ -1546,13 +1546,13 @@
         <v>3.9677</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.1224</v>
+        <v>-0.3571</v>
       </c>
       <c r="T14" t="n">
-        <v>0.1872</v>
+        <v>0.2892</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.3096</v>
+        <v>-0.6463</v>
       </c>
       <c r="V14" t="n">
         <v>0.6745</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2618</v>
+        <v>0.948</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9627</v>
+        <v>1.6769</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.7009</v>
+        <v>-0.7289</v>
       </c>
       <c r="G15" t="n">
         <v>-0.7052</v>
@@ -1624,13 +1624,13 @@
         <v>3.1741</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.2827</v>
+        <v>-0.5966</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.7877999999999999</v>
+        <v>-0.0736</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.4949</v>
+        <v>-0.523</v>
       </c>
       <c r="V15" t="n">
         <v>0.0675</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. HAGENAERS COS</t>
+          <t>A. PILAN PERET</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.285</v>
+        <v>-1.2213</v>
       </c>
       <c r="E16" t="n">
-        <v>2.5137</v>
+        <v>0.8604000000000001</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.7988</v>
+        <v>-2.0817</v>
       </c>
       <c r="G16" t="n">
-        <v>0.8278</v>
+        <v>-0.6091</v>
       </c>
       <c r="H16" t="n">
-        <v>1.4419</v>
+        <v>-1.2296</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.614</v>
+        <v>0.6205000000000001</v>
       </c>
       <c r="J16" t="n">
-        <v>0.9379</v>
+        <v>0.573</v>
       </c>
       <c r="K16" t="n">
-        <v>0.8977000000000001</v>
+        <v>-1.2394</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0402</v>
+        <v>1.8124</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.11</v>
+        <v>-1.1821</v>
       </c>
       <c r="N16" t="n">
-        <v>0.5442</v>
+        <v>0.0098</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.6542</v>
+        <v>-1.1918</v>
       </c>
       <c r="P16" t="n">
         <v>-0.1984</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.9919</v>
+        <v>-1.9838</v>
       </c>
       <c r="R16" t="n">
-        <v>0.7935</v>
+        <v>1.7855</v>
       </c>
       <c r="S16" t="n">
-        <v>2.3002</v>
+        <v>-0.751</v>
       </c>
       <c r="T16" t="n">
-        <v>2.5678</v>
+        <v>-0.1416</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2676</v>
+        <v>-0.6094000000000001</v>
       </c>
       <c r="V16" t="n">
-        <v>-3.2147</v>
+        <v>0.3373</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>2.4129</v>
       </c>
       <c r="X16" t="n">
-        <v>-3.2147</v>
+        <v>-2.0757</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. PILAN PERET</t>
+          <t>J. HAGENAERS COS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.7977</v>
+        <v>-1.8257</v>
       </c>
       <c r="E17" t="n">
-        <v>0.4523</v>
+        <v>1.0853</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.25</v>
+        <v>-2.911</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.6091</v>
+        <v>0.8278</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.2296</v>
+        <v>1.4419</v>
       </c>
       <c r="I17" t="n">
-        <v>0.6205000000000001</v>
+        <v>-0.614</v>
       </c>
       <c r="J17" t="n">
-        <v>0.573</v>
+        <v>0.9379</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.2394</v>
+        <v>0.8977000000000001</v>
       </c>
       <c r="L17" t="n">
-        <v>1.8124</v>
+        <v>0.0402</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.1821</v>
+        <v>-0.11</v>
       </c>
       <c r="N17" t="n">
-        <v>0.0098</v>
+        <v>0.5442</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.1918</v>
+        <v>-0.6542</v>
       </c>
       <c r="P17" t="n">
         <v>-0.1984</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.9838</v>
+        <v>-0.9919</v>
       </c>
       <c r="R17" t="n">
-        <v>1.7855</v>
+        <v>0.7935</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.3275</v>
+        <v>0.7596000000000001</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.5498</v>
+        <v>1.1394</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.7776999999999999</v>
+        <v>-0.3798</v>
       </c>
       <c r="V17" t="n">
-        <v>0.3373</v>
+        <v>-3.2147</v>
       </c>
       <c r="W17" t="n">
-        <v>2.4129</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-2.0757</v>
+        <v>-3.2147</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.9783</v>
+        <v>-1.8482</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.1252</v>
+        <v>-1.0232</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.8531</v>
+        <v>-0.825</v>
       </c>
       <c r="G18" t="n">
         <v>-1.3337</v>
@@ -1858,13 +1858,13 @@
         <v>0.3968</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.1683</v>
+        <v>-0.0382</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.051</v>
+        <v>0.051</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1173</v>
+        <v>-0.0893</v>
       </c>
       <c r="V18" t="n">
         <v>-0.873</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.1429</v>
+        <v>-1.995</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.6683</v>
+        <v>-0.4642</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.4746</v>
+        <v>-1.5307</v>
       </c>
       <c r="G19" t="n">
         <v>-1.0456</v>
@@ -1936,13 +1936,13 @@
         <v>0.5952</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.8196</v>
+        <v>-0.6716</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.7481</v>
+        <v>-0.5441</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.07149999999999999</v>
+        <v>-0.1276</v>
       </c>
       <c r="V19" t="n">
         <v>-0.6745</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.5005</v>
+        <v>-2.7122</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.9167</v>
+        <v>-2.3248</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.5838</v>
+        <v>-0.3874</v>
       </c>
       <c r="G20" t="n">
         <v>-1.9931</v>
@@ -2014,13 +2014,13 @@
         <v>3.3725</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.0107</v>
+        <v>-0.2224</v>
       </c>
       <c r="T20" t="n">
-        <v>1.1168</v>
+        <v>0.7086</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.1275</v>
+        <v>-0.9311</v>
       </c>
       <c r="V20" t="n">
         <v>-2.6789</v>
@@ -2047,10 +2047,10 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.6813</v>
+        <v>-3.2732</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.7914</v>
+        <v>-2.3833</v>
       </c>
       <c r="F21" t="n">
         <v>-0.89</v>
@@ -2092,10 +2092,10 @@
         <v>0.7935</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.9806</v>
+        <v>-0.5725</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.204</v>
+        <v>0.2041</v>
       </c>
       <c r="U21" t="n">
         <v>-0.7766</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.7598</v>
+        <v>-5.5838</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.2364</v>
+        <v>-4.0323</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.5235</v>
+        <v>-1.5515</v>
       </c>
       <c r="G22" t="n">
         <v>-1.2962</v>
@@ -2170,13 +2170,13 @@
         <v>0.9919</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.2057</v>
+        <v>-0.0297</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4251</v>
+        <v>-0.221</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2193</v>
+        <v>0.1913</v>
       </c>
       <c r="V22" t="n">
         <v>-2.0757</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-9.5084</v>
+        <v>-9.5366</v>
       </c>
       <c r="E23" t="n">
         <v>-2.6664</v>
       </c>
       <c r="F23" t="n">
-        <v>-6.8423</v>
+        <v>-6.8702</v>
       </c>
       <c r="G23" t="n">
         <v>-2.56</v>
@@ -2224,16 +2224,16 @@
         <v>4.853399999999999</v>
       </c>
       <c r="K23" t="n">
-        <v>4.481199999999999</v>
+        <v>4.4812</v>
       </c>
       <c r="L23" t="n">
-        <v>0.3725000000000003</v>
+        <v>0.3724999999999999</v>
       </c>
       <c r="M23" t="n">
         <v>-7.4132</v>
       </c>
       <c r="N23" t="n">
-        <v>0.3336000000000001</v>
+        <v>0.3336</v>
       </c>
       <c r="O23" t="n">
         <v>-7.7468</v>
@@ -2248,13 +2248,13 @@
         <v>19.2432</v>
       </c>
       <c r="S23" t="n">
-        <v>-2.478400000000001</v>
+        <v>-2.5064</v>
       </c>
       <c r="T23" t="n">
-        <v>2.4098</v>
+        <v>2.4097</v>
       </c>
       <c r="U23" t="n">
-        <v>-4.8883</v>
+        <v>-4.9164</v>
       </c>
       <c r="V23" t="n">
         <v>-8.8345</v>
